--- a/docs/幸運星幣城_工作分配表.xlsx
+++ b/docs/幸運星幣城_工作分配表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Lucky_star_Casino\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C5B7157-4AB8-46B6-BAA0-916AAE4A2748}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D20538F-D2DF-4FEB-8317-F93F2CC8145E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2722" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2722" uniqueCount="433">
   <si>
     <t>任務編號</t>
   </si>
@@ -1328,6 +1328,10 @@
   </si>
   <si>
     <t>6/19–6/21 放假，不排開發</t>
+  </si>
+  <si>
+    <t>✅ 已完成</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>✅ 已完成</t>
@@ -1763,12 +1767,12 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1778,20 +1782,20 @@
     <xf numFmtId="0" fontId="16" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
@@ -2853,7 +2857,7 @@
         <v>24</v>
       </c>
       <c r="J26" s="33" t="s">
-        <v>31</v>
+        <v>432</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
@@ -5498,7 +5502,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="55" t="s">
         <v>354</v>
       </c>
       <c r="B1" s="54"/>
@@ -6090,7 +6094,7 @@
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="55" t="s">
+      <c r="A22" s="53" t="s">
         <v>355</v>
       </c>
       <c r="B22" s="54"/>
@@ -6105,7 +6109,7 @@
       </c>
     </row>
     <row r="24" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="53" t="s">
+      <c r="A24" s="55" t="s">
         <v>356</v>
       </c>
       <c r="B24" s="54"/>
@@ -6378,7 +6382,7 @@
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34" s="55" t="s">
+      <c r="A34" s="53" t="s">
         <v>355</v>
       </c>
       <c r="B34" s="54"/>
@@ -6393,7 +6397,7 @@
       </c>
     </row>
     <row r="36" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="53" t="s">
+      <c r="A36" s="55" t="s">
         <v>357</v>
       </c>
       <c r="B36" s="54"/>
@@ -6691,7 +6695,7 @@
         <v>4</v>
       </c>
       <c r="I46" s="33" t="s">
-        <v>31</v>
+        <v>432</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
@@ -6811,7 +6815,7 @@
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A51" s="55" t="s">
+      <c r="A51" s="53" t="s">
         <v>355</v>
       </c>
       <c r="B51" s="54"/>
@@ -6826,7 +6830,7 @@
       </c>
     </row>
     <row r="53" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="53" t="s">
+      <c r="A53" s="55" t="s">
         <v>358</v>
       </c>
       <c r="B53" s="54"/>
@@ -7563,7 +7567,7 @@
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A79" s="55" t="s">
+      <c r="A79" s="53" t="s">
         <v>355</v>
       </c>
       <c r="B79" s="54"/>
@@ -7578,7 +7582,7 @@
       </c>
     </row>
     <row r="81" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="53" t="s">
+      <c r="A81" s="55" t="s">
         <v>359</v>
       </c>
       <c r="B81" s="54"/>
@@ -7967,7 +7971,7 @@
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A95" s="55" t="s">
+      <c r="A95" s="53" t="s">
         <v>355</v>
       </c>
       <c r="B95" s="54"/>
@@ -7982,7 +7986,7 @@
       </c>
     </row>
     <row r="97" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="53" t="s">
+      <c r="A97" s="55" t="s">
         <v>360</v>
       </c>
       <c r="B97" s="54"/>
@@ -8081,7 +8085,7 @@
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A101" s="55" t="s">
+      <c r="A101" s="53" t="s">
         <v>355</v>
       </c>
       <c r="B101" s="54"/>
@@ -9751,7 +9755,7 @@
         <v>24</v>
       </c>
       <c r="I63" s="41" t="s">
-        <v>31</v>
+        <v>432</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -10971,7 +10975,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="60" t="s">
         <v>370</v>
       </c>
       <c r="B1" s="54"/>
@@ -10993,24 +10997,24 @@
       <c r="A2" s="61" t="s">
         <v>372</v>
       </c>
-      <c r="B2" s="64"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="62"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="64"/>
       <c r="E2" s="61" t="s">
         <v>373</v>
       </c>
       <c r="F2" s="61" t="s">
         <v>374</v>
       </c>
-      <c r="G2" s="62"/>
+      <c r="G2" s="64"/>
       <c r="H2" s="61" t="s">
         <v>375</v>
       </c>
-      <c r="I2" s="62"/>
+      <c r="I2" s="64"/>
       <c r="J2" s="61" t="s">
         <v>376</v>
       </c>
-      <c r="K2" s="62"/>
+      <c r="K2" s="64"/>
       <c r="L2" s="61" t="s">
         <v>377</v>
       </c>
@@ -11057,7 +11061,7 @@
       </c>
     </row>
     <row r="4" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="53" t="s">
+      <c r="A4" s="55" t="s">
         <v>386</v>
       </c>
       <c r="B4" s="54"/>
@@ -11610,7 +11614,7 @@
       </c>
     </row>
     <row r="24" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="53" t="s">
+      <c r="A24" s="55" t="s">
         <v>392</v>
       </c>
       <c r="B24" s="54"/>
@@ -11842,7 +11846,7 @@
       </c>
     </row>
     <row r="33" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="53" t="s">
+      <c r="A33" s="55" t="s">
         <v>393</v>
       </c>
       <c r="B33" s="54"/>
@@ -12205,11 +12209,11 @@
       <c r="K46" s="22"/>
       <c r="L46" s="22"/>
       <c r="M46" s="33" t="s">
-        <v>31</v>
+        <v>432</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="53" t="s">
+      <c r="A47" s="55" t="s">
         <v>394</v>
       </c>
       <c r="B47" s="54"/>
@@ -12873,7 +12877,7 @@
       </c>
     </row>
     <row r="72" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="53" t="s">
+      <c r="A72" s="55" t="s">
         <v>395</v>
       </c>
       <c r="B72" s="54"/>
@@ -13213,7 +13217,7 @@
       </c>
     </row>
     <row r="85" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="53" t="s">
+      <c r="A85" s="55" t="s">
         <v>396</v>
       </c>
       <c r="B85" s="54"/>
@@ -13283,12 +13287,12 @@
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A88" s="65" t="s">
+      <c r="A88" s="66" t="s">
         <v>397</v>
       </c>
-      <c r="B88" s="64"/>
-      <c r="C88" s="64"/>
-      <c r="D88" s="62"/>
+      <c r="B88" s="63"/>
+      <c r="C88" s="63"/>
+      <c r="D88" s="64"/>
       <c r="E88" s="28">
         <f t="shared" ref="E88:L88" si="0">SUM(E4:E87)</f>
         <v>27</v>
@@ -13323,23 +13327,23 @@
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A89" s="63" t="s">
+      <c r="A89" s="62" t="s">
         <v>398</v>
       </c>
-      <c r="B89" s="64"/>
-      <c r="C89" s="64"/>
-      <c r="D89" s="62"/>
-      <c r="E89" s="63">
+      <c r="B89" s="63"/>
+      <c r="C89" s="63"/>
+      <c r="D89" s="64"/>
+      <c r="E89" s="62">
         <f>SUM(E88:L88)</f>
         <v>304</v>
       </c>
-      <c r="F89" s="64"/>
-      <c r="G89" s="64"/>
-      <c r="H89" s="64"/>
-      <c r="I89" s="64"/>
-      <c r="J89" s="64"/>
-      <c r="K89" s="64"/>
-      <c r="L89" s="62"/>
+      <c r="F89" s="63"/>
+      <c r="G89" s="63"/>
+      <c r="H89" s="63"/>
+      <c r="I89" s="63"/>
+      <c r="J89" s="63"/>
+      <c r="K89" s="63"/>
+      <c r="L89" s="64"/>
     </row>
     <row r="91" spans="1:13" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="25" t="s">
@@ -13356,7 +13360,7 @@
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A92" s="60" t="s">
+      <c r="A92" s="65" t="s">
         <v>403</v>
       </c>
       <c r="B92" s="54"/>
@@ -13373,13 +13377,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="L2"/>
-    <mergeCell ref="A47:L47"/>
-    <mergeCell ref="E89:L89"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="E2"/>
-    <mergeCell ref="A4:L4"/>
     <mergeCell ref="A92:L92"/>
     <mergeCell ref="A24:L24"/>
     <mergeCell ref="F2:G2"/>
@@ -13390,6 +13387,13 @@
     <mergeCell ref="A33:L33"/>
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="A85:L85"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="L2"/>
+    <mergeCell ref="A47:L47"/>
+    <mergeCell ref="E89:L89"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="E2"/>
+    <mergeCell ref="A4:L4"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
